--- a/diseases/d095/2010-2014.xlsx
+++ b/diseases/d095/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15143,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15444,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15745,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16648,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16949,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16760,6 +17250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17648,6 +18153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18454,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18755,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +19056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19128,6 +19658,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +19959,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +20260,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20016,6 +20561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +21163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20904,6 +21464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21496,6 +22066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21792,6 +22367,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22384,6 +22969,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +23270,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23272,6 +23872,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +24173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23864,6 +24474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24752,6 +25377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +25979,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25640,6 +26280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26232,6 +26882,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26528,6 +27183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +27484,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +27785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27416,6 +28086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +28387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28008,6 +28688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +28989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28600,6 +29290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28896,6 +29591,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +29892,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +30193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29784,6 +30494,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +30795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30376,6 +31096,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +31397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30968,6 +31698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31264,6 +31999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31560,6 +32300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31856,6 +32601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32152,6 +32902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32448,6 +33203,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32744,6 +33504,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33040,6 +33805,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33336,6 +34106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33632,6 +34407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33928,6 +34708,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34224,6 +35009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34520,6 +35310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34816,6 +35611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35112,6 +35912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35408,6 +36213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35704,6 +36514,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36000,6 +36815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36296,6 +37116,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36592,6 +37417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36888,6 +37718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37184,6 +38019,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37480,6 +38320,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37776,6 +38621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38072,6 +38922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38368,6 +39223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38664,6 +39524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38960,6 +39825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39256,6 +40126,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39552,6 +40427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39848,6 +40728,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40144,6 +41029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40440,6 +41330,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40736,6 +41631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41032,6 +41932,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41328,6 +42233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41624,6 +42534,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41920,6 +42835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42216,6 +43136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42512,6 +43437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42808,6 +43738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43104,6 +44039,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43400,6 +44340,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43696,6 +44641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43992,6 +44942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44288,6 +45243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44584,6 +45544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44880,6 +45845,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45176,6 +46146,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45472,6 +46447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45768,6 +46748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46064,6 +47049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46360,6 +47350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46656,6 +47651,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46952,6 +47952,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47248,6 +48253,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47544,6 +48554,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47840,6 +48855,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48136,6 +49156,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48432,6 +49457,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48728,6 +49758,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49024,6 +50059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49318,6 +50358,11 @@
       <c r="S330" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO330" t="inlineStr">

--- a/diseases/d095/2010-2014.xlsx
+++ b/diseases/d095/2010-2014.xlsx
@@ -15906,28 +15906,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -16224,28 +16238,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -16542,28 +16570,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -16860,28 +16902,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -17178,28 +17234,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -17496,28 +17566,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -17814,28 +17898,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -18132,28 +18230,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -18450,28 +18562,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -18768,28 +18894,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -19086,28 +19226,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -19404,28 +19558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -19722,28 +19890,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -20040,28 +20222,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -20358,28 +20554,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -20676,28 +20886,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -20994,28 +21218,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -21312,28 +21550,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -21630,28 +21882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -21948,28 +22214,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -22266,28 +22546,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -22584,28 +22878,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -22902,28 +23210,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -23220,28 +23542,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -23538,28 +23874,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -23856,28 +24206,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -24174,28 +24538,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -24492,28 +24870,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -24810,28 +25202,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -25128,28 +25534,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -25446,28 +25866,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -25764,28 +26198,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -26082,28 +26530,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -26400,28 +26862,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -26718,28 +27194,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -27036,28 +27526,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -27354,28 +27858,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -27672,28 +28190,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -27990,28 +28522,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -28308,28 +28854,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -28626,28 +29186,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -28944,28 +29518,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -29262,28 +29850,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -29580,28 +30182,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -29898,28 +30514,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -30216,28 +30846,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -30534,28 +31178,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -30852,28 +31510,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -31170,28 +31842,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -31488,28 +32174,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -31806,28 +32506,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -32124,28 +32838,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
@@ -32442,28 +33170,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -32760,28 +33502,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -33078,28 +33834,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -33396,28 +34166,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -33714,28 +34498,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -34032,28 +34830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -34350,28 +35162,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -34668,28 +35494,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -34986,28 +35826,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -35304,28 +36158,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -35622,28 +36490,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -35940,28 +36822,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -36258,28 +37154,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -36576,28 +37486,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -36894,28 +37818,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
@@ -37212,28 +38150,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -37530,28 +38482,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -38322,28 +39288,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS231" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -39114,28 +40094,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -39906,28 +40900,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -40935,28 +41943,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -42201,28 +43223,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -43230,28 +44266,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -44022,28 +45072,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS259" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
@@ -44814,28 +45878,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -45369,28 +46447,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
@@ -46161,28 +47253,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -46716,28 +47822,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
@@ -47745,28 +48865,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
@@ -48537,28 +49671,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR282" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS282" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
@@ -49329,28 +50477,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR286" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS286" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
@@ -50121,28 +51283,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR290" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS290" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
@@ -50676,28 +51852,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR293" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS293" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
@@ -51231,28 +52421,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR296" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS296" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ296" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
@@ -52023,28 +53227,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR300" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS300" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
@@ -53289,28 +54507,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP306" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR306" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS306" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ306" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
@@ -54555,28 +55787,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR312" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
@@ -55584,28 +56830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR317" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
@@ -56376,28 +57636,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR321" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS321" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV321" t="inlineStr">
@@ -57796,28 +59070,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP328" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR328" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS328" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV328" t="inlineStr">
@@ -58825,28 +60113,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP333" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR333" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS333" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ333" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV333" t="inlineStr">
@@ -59617,28 +60919,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP337" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR337" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS337" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ337" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS337" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV337" t="inlineStr">
@@ -61428,28 +62744,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR346" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS346" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ346" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
@@ -62220,28 +63550,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP350" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR350" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS350" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV350" t="inlineStr">
@@ -63012,28 +64356,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR354" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS354" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ354" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV354" t="inlineStr">
@@ -64041,28 +65399,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR359" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
@@ -64596,28 +65968,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR362" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
@@ -65388,28 +66774,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR366" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ366" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
@@ -66180,28 +67580,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR370" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ370" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
@@ -67446,28 +68860,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR376" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ376" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
@@ -68712,28 +70140,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP382" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR382" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS382" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ382" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV382" t="inlineStr">
@@ -69978,28 +71420,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP388" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR388" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS388" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ388" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU388" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV388" t="inlineStr">
@@ -71007,28 +72463,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP393" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR393" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS393" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ393" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS393" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU393" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV393" t="inlineStr">
@@ -72036,28 +73506,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP398" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR398" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS398" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ398" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU398" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV398" t="inlineStr">
@@ -73065,28 +74549,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP403" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR403" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS403" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ403" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS403" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU403" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV403" t="inlineStr">
@@ -74248,28 +75746,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP409" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR409" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS409" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ409" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU409" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV409" t="inlineStr">
@@ -75040,28 +76552,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR413" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS413" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU413" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV413" t="inlineStr">
@@ -76069,28 +77595,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR418" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS418" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ418" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
@@ -77335,28 +78875,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR424" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS424" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ424" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS424" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
@@ -78127,28 +79681,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR428" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS428" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ428" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
@@ -78919,28 +80487,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR432" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS432" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ432" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
@@ -79711,28 +81293,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR436" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS436" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ436" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
@@ -80503,28 +82099,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP440" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR440" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS440" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ440" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS440" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">
@@ -81295,28 +82905,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP444" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR444" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS444" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ444" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS444" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU444" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV444" t="inlineStr">
@@ -82087,28 +83711,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP448" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR448" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS448" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ448" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU448" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV448" t="inlineStr">
@@ -82879,28 +84517,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO452" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP452" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR452" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS452" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ452" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS452" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU452" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV452" t="inlineStr">
@@ -84145,28 +85797,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP458" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR458" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS458" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ458" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS458" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU458" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV458" t="inlineStr">
@@ -85565,28 +87231,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO465" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP465" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR465" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS465" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ465" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS465" t="inlineStr">
+        <is>
+          <t>HOLD_JP_3c839dd30c421286312b21bb9252</t>
+        </is>
+      </c>
       <c r="AT465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU465" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV465" t="inlineStr">
